--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -747,7 +747,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>111</v>
+        <v>1111</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kacc</t>
+          <t>Alulce</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RLOLCLLELS TL</t>
         </is>
       </c>
     </row>
